--- a/Data.xlsx
+++ b/Data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/00ad163e71df46ba/A Posdoct Conacyt 2026/Experimentacion/AlHfO-PVP/Repositorio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/00ad163e71df46ba/A Posdoct Conacyt 2026/Manuscritos/MOBO AlHfOx/Repositorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{36892B7A-1F6C-4E96-B185-A20D35C5B025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2157B76-0276-4A0D-AE26-DEE28CFD46A2}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{36892B7A-1F6C-4E96-B185-A20D35C5B025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CAFD5414-0D68-4351-A5F7-CF8FE5121ECB}"/>
   <bookViews>
     <workbookView xWindow="-104" yWindow="-104" windowWidth="22326" windowHeight="11947" xr2:uid="{BEB640D2-E66C-411A-ADDB-48C2C2D701D9}"/>
   </bookViews>
@@ -50,16 +50,7 @@
     <t>I_std</t>
   </si>
   <si>
-    <t>Clasificacion</t>
-  </si>
-  <si>
     <t>C (nF/cm2)</t>
-  </si>
-  <si>
-    <t>Factibilidad</t>
-  </si>
-  <si>
-    <t>Muestras</t>
   </si>
   <si>
     <t>-log J</t>
@@ -69,6 +60,15 @@
   </si>
   <si>
     <t>HfOx</t>
+  </si>
+  <si>
+    <t>Sample</t>
+  </si>
+  <si>
+    <t>Class</t>
+  </si>
+  <si>
+    <t>Feasibility</t>
   </si>
 </sst>
 </file>
@@ -150,6 +150,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -478,34 +482,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
-      </c>
-      <c r="D1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
